--- a/Result/profitability/2548.xlsx
+++ b/Result/profitability/2548.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>3.35</v>
       </c>
       <c r="M2" t="n">
-        <v>2.455</v>
+        <v>1.995</v>
       </c>
       <c r="N2" t="n">
-        <v>51.78875</v>
+        <v>51.02</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,16 +780,16 @@
         <v>2.94</v>
       </c>
       <c r="M3" t="n">
-        <v>2.2825</v>
+        <v>2.41625</v>
       </c>
       <c r="N3" t="n">
-        <v>51.87875</v>
+        <v>38.7125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>3.39</v>
       </c>
       <c r="M4" t="n">
-        <v>2.76</v>
+        <v>2.8925</v>
       </c>
       <c r="N4" t="n">
-        <v>39.695</v>
+        <v>31.92125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0875</v>
+        <v>3.0275</v>
       </c>
       <c r="N5" t="n">
-        <v>31.35125</v>
+        <v>31.02</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>3.29</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35875</v>
+        <v>3.30125</v>
       </c>
       <c r="N6" t="n">
-        <v>31.8575</v>
+        <v>32.4625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.53</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4125</v>
+        <v>2.4525</v>
       </c>
       <c r="N7" t="n">
-        <v>33.61375</v>
+        <v>33.81375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>3.49</v>
       </c>
       <c r="M8" t="n">
-        <v>2.80875</v>
+        <v>2.60375</v>
       </c>
       <c r="N8" t="n">
-        <v>34.19125</v>
+        <v>34.66875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>2.725</v>
       </c>
       <c r="N11" t="n">
-        <v>37.49375</v>
+        <v>37.49375000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2548</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1053</v>
+      </c>
+      <c r="E75" t="n">
+        <v>448</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="G75" t="n">
+        <v>280</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.65%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>285</v>
+      </c>
+      <c r="K75" t="n">
+        <v>216</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.11625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>50.5775</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7192982456140351</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1469230769230769</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.4800000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4285714285714286</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.649999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08161379735140128</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
